--- a/artfynd/A 61585-2025 artfynd.xlsx
+++ b/artfynd/A 61585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688290</v>
       </c>
       <c r="B2" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688292</v>
       </c>
       <c r="B3" t="n">
-        <v>78754</v>
+        <v>78755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688291</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129688289</v>
       </c>
       <c r="B5" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129688288</v>
       </c>
       <c r="B6" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61585-2025 artfynd.xlsx
+++ b/artfynd/A 61585-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>132074976</v>
       </c>
       <c r="B7" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 61585-2025 artfynd.xlsx
+++ b/artfynd/A 61585-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>132074976</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 61585-2025 artfynd.xlsx
+++ b/artfynd/A 61585-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>132074976</v>
       </c>
       <c r="B7" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 61585-2025 artfynd.xlsx
+++ b/artfynd/A 61585-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>132074976</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 61585-2025 artfynd.xlsx
+++ b/artfynd/A 61585-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688292</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132074909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132074976</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224230</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224231</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688243</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688288</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1558,6 +1598,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688289</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,6 +1709,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688291</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,8 +1820,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688290</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>